--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.52544463378414</v>
+        <v>5.610384752989923</v>
       </c>
       <c r="D2" t="n">
-        <v>7.732822988553989</v>
+        <v>1.256583735640023</v>
       </c>
       <c r="E2" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F2" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.784197822035879</v>
+        <v>0.9399321460808304</v>
       </c>
       <c r="D3" t="n">
-        <v>36.79023755605107</v>
+        <v>5.9784136028583</v>
       </c>
       <c r="E3" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F3" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.63548716295183</v>
+        <v>4.978266663979673</v>
       </c>
       <c r="D4" t="n">
-        <v>25.78277694945574</v>
+        <v>4.189701254286558</v>
       </c>
       <c r="E4" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F4" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.15659112821552</v>
+        <v>3.925446058335023</v>
       </c>
       <c r="D5" t="n">
-        <v>17.99836706312973</v>
+        <v>2.924734647758581</v>
       </c>
       <c r="E5" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F5" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.38843438620099</v>
+        <v>4.938120587757662</v>
       </c>
       <c r="D6" t="n">
-        <v>53.79906840502771</v>
+        <v>8.742348615817003</v>
       </c>
       <c r="E6" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F6" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.64741050325037</v>
+        <v>6.117704206778185</v>
       </c>
       <c r="D7" t="n">
-        <v>41.21155082212395</v>
+        <v>6.696877008595141</v>
       </c>
       <c r="E7" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F7" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.45341247071078</v>
+        <v>3.486179526490502</v>
       </c>
       <c r="D8" t="n">
-        <v>19.61912700441333</v>
+        <v>3.188108138217167</v>
       </c>
       <c r="E8" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F8" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.05142658014306</v>
+        <v>10.73335681927325</v>
       </c>
       <c r="D9" t="n">
-        <v>63.33614862669988</v>
+        <v>10.29212415183873</v>
       </c>
       <c r="E9" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F9" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>63.26285213810232</v>
+        <v>10.28021347244163</v>
       </c>
       <c r="D10" t="n">
-        <v>20.97059401606816</v>
+        <v>3.407721527611076</v>
       </c>
       <c r="E10" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F10" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>70.1336924235778</v>
+        <v>11.39672501883139</v>
       </c>
       <c r="D11" t="n">
-        <v>56.2850133688849</v>
+        <v>9.146314672443797</v>
       </c>
       <c r="E11" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F11" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>79.48994850185484</v>
+        <v>12.91711663155141</v>
       </c>
       <c r="D12" t="n">
-        <v>21.03835313799016</v>
+        <v>3.418732384923402</v>
       </c>
       <c r="E12" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F12" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>90.23611855337609</v>
+        <v>14.66336926492361</v>
       </c>
       <c r="D13" t="n">
-        <v>31.29963509519804</v>
+        <v>5.086190702969682</v>
       </c>
       <c r="E13" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F13" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>88.78728336683912</v>
+        <v>14.42793354711136</v>
       </c>
       <c r="D14" t="n">
-        <v>51.59650289100841</v>
+        <v>8.384431719788866</v>
       </c>
       <c r="E14" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F14" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>101.085095451222</v>
+        <v>16.42632801082357</v>
       </c>
       <c r="D15" t="n">
-        <v>65.28532918502086</v>
+        <v>10.60886599256589</v>
       </c>
       <c r="E15" t="n">
-        <v>29.1487768217117</v>
+        <v>4.736676233528152</v>
       </c>
       <c r="F15" t="n">
-        <v>18.06021810697766</v>
+        <v>2.93478544238387</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
